--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125507938</v>
       </c>
       <c r="B2" t="n">
-        <v>57629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,134 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126127813</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Alstervik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>420048</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6587968</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125507938</v>
       </c>
       <c r="B2" t="n">
-        <v>57645</v>
+        <v>57646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>126127813</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>126127813</v>
       </c>
       <c r="B3" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>126127813</v>
       </c>
       <c r="B3" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>126127813</v>
       </c>
       <c r="B3" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>126127813</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>126127813</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125507938</v>
+        <v>133302730</v>
       </c>
       <c r="B2" t="n">
-        <v>57646</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,31 +708,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alstervik, Vrm</t>
+          <t>Ringsåker, Ringsåker, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420186</v>
+        <v>420029</v>
       </c>
       <c r="R2" t="n">
-        <v>6588150</v>
+        <v>6587756</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,66 +780,76 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Matilda Elgerud</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Matilda Elgerud</t>
+          <t>Camilla Berglund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126127813</v>
+        <v>126127820</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>45033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>102366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsmetallvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Adscita statices</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -853,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420048</v>
+        <v>420133</v>
       </c>
       <c r="R3" t="n">
-        <v>6587968</v>
+        <v>6588131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,6 +909,11 @@
           <t>14:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på smörblomma</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -923,6 +936,872 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119440599</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43251</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102923</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettkantad guldvinge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycaena hippothoe</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ringsåker, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>420142</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6588001</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Karlstad kommun - Brungräsfjäril stockfallet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125507938</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alstervik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>420186</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6588150</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125508335</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>420017</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6587978</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126127802</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alstervik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>420103</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6588002</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126127810</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Alstervik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>420117</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6588037</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126127813</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alstervik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>420048</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6587968</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131379215</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Karlstad-Väse, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>420092</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6588010</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47561-2023 artfynd.xlsx
+++ b/artfynd/A 47561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133302730</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,6 +946,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126127820</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1061,6 +1076,11 @@
           <t>Karlstad kommun - Brungräsfjäril stockfallet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119440599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1184,6 +1204,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125507938</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1312,6 +1337,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125508335</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1440,6 +1470,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126127802</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1568,6 +1603,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126127810</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1696,6 +1736,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126127813</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1802,8 +1847,24 @@
           <t>Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131379215</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>